--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131737970</v>
+        <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57911</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673750</v>
+        <v>673746</v>
       </c>
       <c r="R2" t="n">
-        <v>7031859</v>
+        <v>7031864</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131736490</v>
+        <v>131737970</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -805,16 +805,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Österbacke Nordost, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673746</v>
+        <v>673750</v>
       </c>
       <c r="R3" t="n">
-        <v>7031864</v>
+        <v>7031859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131737970</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>57915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131737970</v>
       </c>
       <c r="B3" t="n">
-        <v>57915</v>
+        <v>57917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131737970</v>
       </c>
       <c r="B3" t="n">
-        <v>57917</v>
+        <v>57920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131737970</v>
       </c>
       <c r="B3" t="n">
-        <v>57920</v>
+        <v>57925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131737970</v>
       </c>
       <c r="B3" t="n">
-        <v>57925</v>
+        <v>57927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131736490</v>
       </c>
       <c r="B2" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131737970</v>
       </c>
       <c r="B3" t="n">
-        <v>57927</v>
+        <v>57961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61395-2025 artfynd.xlsx
+++ b/artfynd/A 61395-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,8 +892,17 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736490</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>